--- a/assets/xlsx/testdhai.xlsx
+++ b/assets/xlsx/testdhai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\migrasiplaywright12345\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738360B0-8E03-4CBA-9F25-A9F3349BAB63}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C22CA8C-6209-4EDE-A8D6-F0FD279BC371}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,22 +34,22 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Halo! Saya Luna, asisten virtual dari Botika yang siap membantu Anda dengan informasi terkait pariwisata. Apakah ada yang bisa saya bantu hari ini?</t>
-  </si>
-  <si>
-    <t>tanya sapa</t>
-  </si>
-  <si>
-    <t>siapa kamu?</t>
-  </si>
-  <si>
-    <t>apa rekomendasi wisata di jogja</t>
-  </si>
-  <si>
-    <t>Di Yogyakarta, Anda bisa mengunjungi Situs Warungboto, yang juga dikenal sebagai Pesanggrahan Rejowinangun. Tempat ini menawarkan pengalaman wisata sejarah dengan nuansa Jawa kuno. Selain itu, Pantai Parangtritis adalah destinasi ikonik di Jogja yang menawarkan berbagai aktivitas seperti naik delman, ATV, dan jeep. Apakah ada tempat lain yang ingin Anda ketahui?</t>
-  </si>
-  <si>
-    <t>wisata jogja</t>
+    <t>Asuransi Jiwa</t>
+  </si>
+  <si>
+    <t>Apa itu asuransi jiwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenis asuransi ini memberikan perlindungan finansial terhadap risiko kehidupan dan kematian pemegang polis. Karakteristik utama asuransi jiwa adalah pemberian manfaat berupa uang pertanggungan kepada ahli waris jika pemegang polis berpulang. Apabila pemegang polis masih hidup dalam jangka waktu yang ditentukan, mereka akan mendapatkan manfaat dalam bentuk nilai tunai.Manfaat dan perlindungan yang diberikan asuransi jiwa berupa uang pertanggungan yang bisa digunakan untuk memenuhi kebutuhan sehari-hari.    </t>
+  </si>
+  <si>
+    <t>Asuransi Kesehatan</t>
+  </si>
+  <si>
+    <t>Apa itu asuransi kesehatan</t>
+  </si>
+  <si>
+    <t>Asuransi kesehatan merupakan jenis asuransi yang memberikan perlindungan finansial ketika mengalami masalah kesehatan. Asuransi ini berguna ketika nasabah menjalani rawat inap, operasi, maupun bentuk perawatan lainnya yang dilakukan di rumah sakit. Asuransi kesehatan sangat penting untuk dimiliki karena bisa melindungi aset atau keuangan nasabah pada saat melakukan pengobatan dengan biaya yang tidak sedikit.</t>
   </si>
 </sst>
 </file>
@@ -416,13 +416,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -430,13 +430,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/assets/xlsx/testdhai.xlsx
+++ b/assets/xlsx/testdhai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\migrasiplaywright12345\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C22CA8C-6209-4EDE-A8D6-F0FD279BC371}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071A1C15-5045-44E9-9B07-0B856EA07944}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>No</t>
   </si>
@@ -34,33 +34,53 @@
     <t>Context</t>
   </si>
   <si>
-    <t>Asuransi Jiwa</t>
-  </si>
-  <si>
-    <t>Apa itu asuransi jiwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jenis asuransi ini memberikan perlindungan finansial terhadap risiko kehidupan dan kematian pemegang polis. Karakteristik utama asuransi jiwa adalah pemberian manfaat berupa uang pertanggungan kepada ahli waris jika pemegang polis berpulang. Apabila pemegang polis masih hidup dalam jangka waktu yang ditentukan, mereka akan mendapatkan manfaat dalam bentuk nilai tunai.Manfaat dan perlindungan yang diberikan asuransi jiwa berupa uang pertanggungan yang bisa digunakan untuk memenuhi kebutuhan sehari-hari.    </t>
-  </si>
-  <si>
-    <t>Asuransi Kesehatan</t>
-  </si>
-  <si>
-    <t>Apa itu asuransi kesehatan</t>
-  </si>
-  <si>
-    <t>Asuransi kesehatan merupakan jenis asuransi yang memberikan perlindungan finansial ketika mengalami masalah kesehatan. Asuransi ini berguna ketika nasabah menjalani rawat inap, operasi, maupun bentuk perawatan lainnya yang dilakukan di rumah sakit. Asuransi kesehatan sangat penting untuk dimiliki karena bisa melindungi aset atau keuangan nasabah pada saat melakukan pengobatan dengan biaya yang tidak sedikit.</t>
+    <t>rekomendasi tempat wisata?</t>
+  </si>
+  <si>
+    <t>Tentu! Beberapa destinasi wisata yang bisa Anda kunjungi di Indonesia adalah Borobudur, Danau Toba, Labuan Bajo, Mandalika, dan Likupang. Jika Anda tertarik dengan wisata sejarah, Situs Warungboto di Yogyakarta juga menarik untuk dikunjungi. Apakah ada destinasi tertentu yang Anda ingin tahu lebih lanjut?</t>
+  </si>
+  <si>
+    <t>wisata di jogja mana yang oke?</t>
+  </si>
+  <si>
+    <t>rekomendasi wisata</t>
+  </si>
+  <si>
+    <t>wisata jogja</t>
+  </si>
+  <si>
+    <t>Di Yogyakarta, Anda bisa mengunjungi Candi Borobudur yang merupakan salah satu dari 7 keajaiban dunia. Selain itu, Pantai Parangtritis juga menawarkan pengalaman seru dengan berbagai aktivitas seperti naik delman, ATV, dan jeep. Situs Warungboto juga menarik untuk wisata sejarah. Apakah ada tempat lain yang ingin Anda ketahui?</t>
+  </si>
+  <si>
+    <t>pantai gunung kidul ada di mana saja?</t>
+  </si>
+  <si>
+    <t>pantai gunung kidul</t>
+  </si>
+  <si>
+    <t>Di Gunung Kidul, Yogyakarta, terdapat beberapa pantai yang menarik untuk dikunjungi. Salah satunya adalah Pantai Timang yang terkenal dengan gondolanya yang memacu adrenalin. Selain itu, ada juga Pantai Indrayanti, Pantai Drini, dan Pantai Baron yang menawarkan pemandangan indah dan suasana yang menenangkan. Apakah Anda tertarik untuk mengunjungi salah satu pantai tersebut?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Manrope"/>
     </font>
   </fonts>
   <fills count="2">
@@ -83,8 +103,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,58 +411,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="115.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="115.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/xlsx/testdhai.xlsx
+++ b/assets/xlsx/testdhai.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21629"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\migrasiplaywright12345\assets\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071A1C15-5045-44E9-9B07-0B856EA07944}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Worksheet"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -34,28 +28,28 @@
     <t>Context</t>
   </si>
   <si>
+    <t>rekomendasi wisata</t>
+  </si>
+  <si>
     <t>rekomendasi tempat wisata?</t>
   </si>
   <si>
     <t>Tentu! Beberapa destinasi wisata yang bisa Anda kunjungi di Indonesia adalah Borobudur, Danau Toba, Labuan Bajo, Mandalika, dan Likupang. Jika Anda tertarik dengan wisata sejarah, Situs Warungboto di Yogyakarta juga menarik untuk dikunjungi. Apakah ada destinasi tertentu yang Anda ingin tahu lebih lanjut?</t>
   </si>
   <si>
+    <t>wisata jogja</t>
+  </si>
+  <si>
     <t>wisata di jogja mana yang oke?</t>
   </si>
   <si>
-    <t>rekomendasi wisata</t>
-  </si>
-  <si>
-    <t>wisata jogja</t>
-  </si>
-  <si>
     <t>Di Yogyakarta, Anda bisa mengunjungi Candi Borobudur yang merupakan salah satu dari 7 keajaiban dunia. Selain itu, Pantai Parangtritis juga menawarkan pengalaman seru dengan berbagai aktivitas seperti naik delman, ATV, dan jeep. Situs Warungboto juga menarik untuk wisata sejarah. Apakah ada tempat lain yang ingin Anda ketahui?</t>
   </si>
   <si>
+    <t>pantai gunung kidul</t>
+  </si>
+  <si>
     <t>pantai gunung kidul ada di mana saja?</t>
-  </si>
-  <si>
-    <t>pantai gunung kidul</t>
   </si>
   <si>
     <t>Di Gunung Kidul, Yogyakarta, terdapat beberapa pantai yang menarik untuk dikunjungi. Salah satunya adalah Pantai Timang yang terkenal dengan gondolanya yang memacu adrenalin. Selain itu, ada juga Pantai Indrayanti, Pantai Drini, dan Pantai Baron yang menawarkan pemandangan indah dan suasana yang menenangkan. Apakah Anda tertarik untuk mengunjungi salah satu pantai tersebut?</t>
@@ -64,23 +58,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Manrope"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,7 +89,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -103,22 +108,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="7">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -129,10 +147,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -170,71 +188,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,54 +276,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -315,7 +332,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -324,7 +341,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -333,7 +350,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -341,10 +358,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -373,7 +390,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -386,13 +403,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -410,76 +426,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="115.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" style="5" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="26.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="115.57642857142856" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>